--- a/Jobdata.xlsx
+++ b/Jobdata.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3594" uniqueCount="1163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3603" uniqueCount="1163">
   <si>
     <t>Update Date</t>
   </si>
@@ -4474,7 +4474,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M278"/>
+  <dimension ref="A1:M279"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.6666666666667" customWidth="1"/>
@@ -15887,6 +15887,38 @@
       </c>
       <c r="M278" s="1" t="s">
         <v>1033</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13">
+      <c r="A279" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E279" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F279" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G279" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H279" s="4">
+        <v>46173</v>
+      </c>
+      <c r="I279" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J279" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
